--- a/docs/StructureDefinition-BRAlergiaReacaoAdversa-1.0.xlsx
+++ b/docs/StructureDefinition-BRAlergiaReacaoAdversa-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1155,7 +1155,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1233,7 +1233,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1318,7 +1318,7 @@
     <t>AllergyIntolerance.patient.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1358,7 +1358,7 @@
     <t>AllergyIntolerance.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1418,7 +1418,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1441,7 +1441,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1506,7 +1506,7 @@
     <t>AllergyIntolerance.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1616,7 +1616,7 @@
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -1744,7 +1744,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>
@@ -2240,7 +2240,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>237</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>256</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>265</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>278</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>288</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>292</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>304</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>314</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>331</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>338</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>433</v>
       </c>
@@ -10991,7 +10991,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>466</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>492</v>
       </c>
@@ -14095,12 +14095,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM108">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
